--- a/rental_data.xlsx
+++ b/rental_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kapelan/Downloads/NaviBot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E19DA6F8-D074-3D44-9CA7-F6C2631A51D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BD5FB9-9E49-EA4D-9BA2-4A0AAC0ABE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="140" yWindow="640" windowWidth="28480" windowHeight="17180" xr2:uid="{EC73D2C8-4BF9-5345-9D53-039007822FE8}"/>
+    <workbookView xWindow="0" yWindow="560" windowWidth="28480" windowHeight="17180" activeTab="1" xr2:uid="{EC73D2C8-4BF9-5345-9D53-039007822FE8}"/>
   </bookViews>
   <sheets>
     <sheet name="Теплоходы" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5311" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5478" uniqueCount="174">
   <si>
     <t>Название теплохода</t>
   </si>
@@ -540,6 +540,24 @@
   </si>
   <si>
     <t>https://teplohod-restoran.ru/product/florenciya/</t>
+  </si>
+  <si>
+    <t>Ряпушка</t>
+  </si>
+  <si>
+    <t>https://teplohod-restoran.ru/product/ryapushka/</t>
+  </si>
+  <si>
+    <t>Талисман</t>
+  </si>
+  <si>
+    <t>https://teplohod-restoran.ru/product/talisman/</t>
+  </si>
+  <si>
+    <t>11:00 - 22:00</t>
+  </si>
+  <si>
+    <t>22:00 - 11:00</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1263,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D3B44BE-0386-0045-804F-512BE6AB2629}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" style="1" customWidth="1"/>
@@ -2375,6 +2393,46 @@
       </c>
       <c r="F56" s="6">
         <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C57" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="D57" s="1">
+        <v>10000</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C58" s="40" t="s">
+        <v>163</v>
+      </c>
+      <c r="D58" s="1">
+        <v>10000</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2434,6 +2492,8 @@
     <hyperlink ref="B25" r:id="rId52" xr:uid="{06ACCB8F-7DC4-B246-87BF-7A3E3D727827}"/>
     <hyperlink ref="B14" r:id="rId53" xr:uid="{B0859EA4-9569-4D49-B3A1-397D632EB8DE}"/>
     <hyperlink ref="B10" r:id="rId54" xr:uid="{D3D86428-BBF3-7A4B-ABD0-44FA94C5EBD3}"/>
+    <hyperlink ref="B57" r:id="rId55" xr:uid="{A0EE9FEB-97E9-4247-9009-C7E0FCDD8C4A}"/>
+    <hyperlink ref="B58" r:id="rId56" xr:uid="{52430A9F-BE7F-5F4D-AEB1-F6A05562BA4A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2442,7 +2502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{123645B5-8653-634D-8B6E-36FD1C9E7A64}">
-  <dimension ref="A1:H1271"/>
+  <dimension ref="A1:H1311"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.5" style="7" customWidth="1"/>
@@ -17582,7 +17642,7 @@
         <v>20</v>
       </c>
       <c r="C658" s="65">
-        <v>45816</v>
+        <v>45814</v>
       </c>
       <c r="D658" s="65">
         <v>45850</v>
@@ -17605,7 +17665,7 @@
         <v>20</v>
       </c>
       <c r="C659" s="65">
-        <v>45816</v>
+        <v>45814</v>
       </c>
       <c r="D659" s="65">
         <v>45850</v>
@@ -17628,7 +17688,7 @@
         <v>20</v>
       </c>
       <c r="C660" s="65">
-        <v>45816</v>
+        <v>45814</v>
       </c>
       <c r="D660" s="65">
         <v>45850</v>
@@ -17651,7 +17711,7 @@
         <v>20</v>
       </c>
       <c r="C661" s="65">
-        <v>45816</v>
+        <v>45814</v>
       </c>
       <c r="D661" s="65">
         <v>45850</v>
@@ -31694,6 +31754,926 @@
       </c>
       <c r="G1271" s="29">
         <v>70000</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1272" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1272" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1272" s="44">
+        <v>45658</v>
+      </c>
+      <c r="D1272" s="44">
+        <v>45791</v>
+      </c>
+      <c r="E1272" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1272" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1272" s="8">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1273" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1273" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1273" s="44">
+        <v>45658</v>
+      </c>
+      <c r="D1273" s="44">
+        <v>45791</v>
+      </c>
+      <c r="E1273" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1273" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1273" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1274" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1274" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1274" s="44">
+        <v>45658</v>
+      </c>
+      <c r="D1274" s="44">
+        <v>45791</v>
+      </c>
+      <c r="E1274" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1274" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1274" s="8">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1275" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1275" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1275" s="44">
+        <v>45658</v>
+      </c>
+      <c r="D1275" s="44">
+        <v>45791</v>
+      </c>
+      <c r="E1275" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1275" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1275" s="8">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:7" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1276" s="80" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1276" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1276" s="81">
+        <v>45905</v>
+      </c>
+      <c r="D1276" s="81">
+        <v>46022</v>
+      </c>
+      <c r="E1276" s="95" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1276" s="80" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1276" s="80">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:7" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1277" s="80" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1277" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1277" s="81">
+        <v>45905</v>
+      </c>
+      <c r="D1277" s="81">
+        <v>46022</v>
+      </c>
+      <c r="E1277" s="95" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1277" s="80" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1277" s="80">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:7" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1278" s="80" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1278" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1278" s="81">
+        <v>45905</v>
+      </c>
+      <c r="D1278" s="81">
+        <v>46022</v>
+      </c>
+      <c r="E1278" s="97" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1278" s="80" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1278" s="80">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:7" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1279" s="80" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1279" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1279" s="81">
+        <v>45905</v>
+      </c>
+      <c r="D1279" s="81">
+        <v>46022</v>
+      </c>
+      <c r="E1279" s="97" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1279" s="80" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1279" s="80">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:7" s="47" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1280" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1280" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1280" s="66">
+        <v>45792</v>
+      </c>
+      <c r="D1280" s="66">
+        <v>45817</v>
+      </c>
+      <c r="E1280" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1280" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1280" s="47">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:7" s="47" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1281" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1281" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1281" s="66">
+        <v>45792</v>
+      </c>
+      <c r="D1281" s="66">
+        <v>45817</v>
+      </c>
+      <c r="E1281" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1281" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1281" s="47">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:7" s="47" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1282" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1282" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1282" s="66">
+        <v>45792</v>
+      </c>
+      <c r="D1282" s="66">
+        <v>45817</v>
+      </c>
+      <c r="E1282" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1282" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1282" s="47">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:7" s="47" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1283" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1283" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1283" s="66">
+        <v>45792</v>
+      </c>
+      <c r="D1283" s="66">
+        <v>45817</v>
+      </c>
+      <c r="E1283" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1283" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1283" s="47">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1284" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1284" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1284" s="64">
+        <v>45839</v>
+      </c>
+      <c r="D1284" s="64">
+        <v>45904</v>
+      </c>
+      <c r="E1284" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1284" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1284" s="11">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1285" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1285" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1285" s="64">
+        <v>45839</v>
+      </c>
+      <c r="D1285" s="64">
+        <v>45904</v>
+      </c>
+      <c r="E1285" s="42" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1285" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1285" s="11">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1286" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1286" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1286" s="64">
+        <v>45839</v>
+      </c>
+      <c r="D1286" s="64">
+        <v>45904</v>
+      </c>
+      <c r="E1286" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1286" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1286" s="11">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1287" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1287" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1287" s="64">
+        <v>45839</v>
+      </c>
+      <c r="D1287" s="64">
+        <v>45904</v>
+      </c>
+      <c r="E1287" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1287" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1287" s="11">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1288" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1288" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1288" s="65">
+        <v>45818</v>
+      </c>
+      <c r="D1288" s="65">
+        <v>45838</v>
+      </c>
+      <c r="E1288" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1288" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1288" s="17">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1289" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1289" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1289" s="65">
+        <v>45818</v>
+      </c>
+      <c r="D1289" s="65">
+        <v>45838</v>
+      </c>
+      <c r="E1289" s="43" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1289" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1289" s="17">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1290" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1290" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1290" s="65">
+        <v>45818</v>
+      </c>
+      <c r="D1290" s="65">
+        <v>45838</v>
+      </c>
+      <c r="E1290" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1290" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1290" s="17">
+        <v>80000</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1291" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1291" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1291" s="65">
+        <v>45818</v>
+      </c>
+      <c r="D1291" s="65">
+        <v>45838</v>
+      </c>
+      <c r="E1291" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F1291" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1291" s="17">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1292" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1292" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1292" s="44">
+        <v>45658</v>
+      </c>
+      <c r="D1292" s="44">
+        <v>45791</v>
+      </c>
+      <c r="E1292" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1292" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1292" s="8">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1293" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1293" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1293" s="44">
+        <v>45658</v>
+      </c>
+      <c r="D1293" s="44">
+        <v>45791</v>
+      </c>
+      <c r="E1293" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1293" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1293" s="8">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1294" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1294" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1294" s="44">
+        <v>45658</v>
+      </c>
+      <c r="D1294" s="44">
+        <v>45791</v>
+      </c>
+      <c r="E1294" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1294" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1294" s="8">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1295" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1295" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1295" s="44">
+        <v>45658</v>
+      </c>
+      <c r="D1295" s="44">
+        <v>45791</v>
+      </c>
+      <c r="E1295" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1295" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1295" s="8">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:7" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1296" s="80" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1296" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1296" s="81">
+        <v>45905</v>
+      </c>
+      <c r="D1296" s="81">
+        <v>46022</v>
+      </c>
+      <c r="E1296" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1296" s="80" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1296" s="80">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:7" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1297" s="80" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1297" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1297" s="81">
+        <v>45905</v>
+      </c>
+      <c r="D1297" s="81">
+        <v>46022</v>
+      </c>
+      <c r="E1297" s="80" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1297" s="80" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1297" s="80">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:7" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1298" s="80" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1298" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1298" s="81">
+        <v>45905</v>
+      </c>
+      <c r="D1298" s="81">
+        <v>46022</v>
+      </c>
+      <c r="E1298" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1298" s="80" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1298" s="80">
+        <v>35000</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:7" s="80" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1299" s="80" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1299" s="80" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1299" s="81">
+        <v>45905</v>
+      </c>
+      <c r="D1299" s="81">
+        <v>46022</v>
+      </c>
+      <c r="E1299" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1299" s="80" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1299" s="80">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:7" s="47" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1300" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1300" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1300" s="66">
+        <v>45792</v>
+      </c>
+      <c r="D1300" s="66">
+        <v>45817</v>
+      </c>
+      <c r="E1300" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1300" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1300" s="47">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:7" s="47" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1301" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1301" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1301" s="66">
+        <v>45792</v>
+      </c>
+      <c r="D1301" s="66">
+        <v>45817</v>
+      </c>
+      <c r="E1301" s="47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1301" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1301" s="47">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:7" s="47" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1302" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1302" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1302" s="66">
+        <v>45792</v>
+      </c>
+      <c r="D1302" s="66">
+        <v>45817</v>
+      </c>
+      <c r="E1302" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1302" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1302" s="47">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:7" s="47" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1303" s="47" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1303" s="47" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1303" s="66">
+        <v>45792</v>
+      </c>
+      <c r="D1303" s="66">
+        <v>45817</v>
+      </c>
+      <c r="E1303" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1303" s="47" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1303" s="47">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1304" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1304" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1304" s="64">
+        <v>45846</v>
+      </c>
+      <c r="D1304" s="64">
+        <v>45904</v>
+      </c>
+      <c r="E1304" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1304" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1304" s="11">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1305" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1305" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1305" s="64">
+        <v>45846</v>
+      </c>
+      <c r="D1305" s="64">
+        <v>45904</v>
+      </c>
+      <c r="E1305" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1305" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1305" s="11">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1306" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1306" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1306" s="64">
+        <v>45846</v>
+      </c>
+      <c r="D1306" s="64">
+        <v>45904</v>
+      </c>
+      <c r="E1306" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1306" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1306" s="11">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:7" s="11" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1307" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1307" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1307" s="64">
+        <v>45846</v>
+      </c>
+      <c r="D1307" s="64">
+        <v>45904</v>
+      </c>
+      <c r="E1307" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1307" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1307" s="11">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1308" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1308" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1308" s="65">
+        <v>45818</v>
+      </c>
+      <c r="D1308" s="65">
+        <v>45845</v>
+      </c>
+      <c r="E1308" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1308" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1308" s="17">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1309" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1309" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1309" s="65">
+        <v>45818</v>
+      </c>
+      <c r="D1309" s="65">
+        <v>45845</v>
+      </c>
+      <c r="E1309" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1309" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1309" s="17">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1310" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1310" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1310" s="65">
+        <v>45818</v>
+      </c>
+      <c r="D1310" s="65">
+        <v>45845</v>
+      </c>
+      <c r="E1310" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1310" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="G1310" s="17">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1311" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1311" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1311" s="65">
+        <v>45818</v>
+      </c>
+      <c r="D1311" s="65">
+        <v>45845</v>
+      </c>
+      <c r="E1311" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1311" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1311" s="17">
+        <v>50000</v>
       </c>
     </row>
   </sheetData>

--- a/rental_data.xlsx
+++ b/rental_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kapelan/Downloads/NaviBot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3BD5FB9-9E49-EA4D-9BA2-4A0AAC0ABE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD161F6-7663-C644-A66D-13A9A6E09486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="560" windowWidth="28480" windowHeight="17180" activeTab="1" xr2:uid="{EC73D2C8-4BF9-5345-9D53-039007822FE8}"/>
   </bookViews>

--- a/rental_data.xlsx
+++ b/rental_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10309"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kapelan/Downloads/NaviBot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CD161F6-7663-C644-A66D-13A9A6E09486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1834C75-236A-F14D-8A33-16008606D8B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="560" windowWidth="28480" windowHeight="17180" activeTab="1" xr2:uid="{EC73D2C8-4BF9-5345-9D53-039007822FE8}"/>
   </bookViews>
